--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2038,6 +2038,29 @@
         <v>152.2</v>
       </c>
     </row>
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>46252.25042497685</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="6">
+        <v>17</v>
+      </c>
+      <c r="D18" s="6">
+        <v>45</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>159.6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2061,6 +2061,29 @@
         <v>159.6</v>
       </c>
     </row>
+    <row r="19" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>46252.29064265046</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="4">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4">
+        <v>45</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>151.9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2084,6 +2084,29 @@
         <v>151.9</v>
       </c>
     </row>
+    <row r="20" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>46252.32494453704</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="6">
+        <v>17</v>
+      </c>
+      <c r="D20" s="6">
+        <v>45</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <v>149.7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2107,6 +2107,29 @@
         <v>149.7</v>
       </c>
     </row>
+    <row r="21" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>46252.367560810184</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="4">
+        <v>17</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>149.5</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2130,6 +2130,29 @@
         <v>149.5</v>
       </c>
     </row>
+    <row r="22" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <v>46252.40549311343</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="6">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2153,6 +2153,29 @@
         <v>152</v>
       </c>
     </row>
+    <row r="23" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>46252.44434782407</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="4">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4">
+        <v>46</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>154.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2176,6 +2176,29 @@
         <v>154.4</v>
       </c>
     </row>
+    <row r="24" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>46252.46634255787</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="6">
+        <v>17</v>
+      </c>
+      <c r="D24" s="6">
+        <v>46</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <v>153.4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2199,6 +2199,29 @@
         <v>153.4</v>
       </c>
     </row>
+    <row r="25" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>46252.48330226852</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="4">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2222,6 +2222,29 @@
         <v>155</v>
       </c>
     </row>
+    <row r="26" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>46252.49732729167</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="6">
+        <v>17</v>
+      </c>
+      <c r="D26" s="6">
+        <v>46</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <v>149.7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2245,6 +2245,29 @@
         <v>149.7</v>
       </c>
     </row>
+    <row r="27" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>46252.54355082176</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="4">
+        <v>17</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>153.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">

--- a/outputs/job-monitor/Job_Monitor.xlsx
+++ b/outputs/job-monitor/Job_Monitor.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="123">
   <si>
     <t>Career Page Monitor — Company Registry</t>
   </si>
@@ -1649,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2268,6 +2268,29 @@
         <v>153.8</v>
       </c>
     </row>
+    <row r="28" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>46252.57797991898</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="6">
+        <v>17</v>
+      </c>
+      <c r="D28" s="6">
+        <v>46</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <v>165.9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:G2"/>
   <mergeCells count="1">
